--- a/xls/Simulacao_exemplo2.xlsx
+++ b/xls/Simulacao_exemplo2.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\OneDrive\Documentos\estatistica2024\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\OneDrive\Documentos\estatistica2025\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D0E5AC-7E3A-4DE3-BAE8-F6F85CA4D205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="5370" windowWidth="20730" windowHeight="5280"/>
+    <workbookView xWindow="675" yWindow="2085" windowWidth="26610" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exemplo 2" sheetId="9" r:id="rId1"/>
     <sheet name="Monte Carlo" sheetId="17" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>Urna A</t>
   </si>
@@ -103,17 +117,20 @@
     <t>FR</t>
   </si>
   <si>
-    <t>#http://www.dpi.inpe.br/~camilo/estatistica</t>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2025</t>
   </si>
   <si>
-    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2024</t>
+    <t>#http://urlib.net/8JMKD2USNRW34T/4D6DMD2</t>
+  </si>
+  <si>
+    <t>#https://cdrenno.github.io/Estatistica/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -127,13 +144,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -163,7 +173,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -186,7 +196,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -228,7 +237,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
@@ -306,6 +315,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-437F-4DA7-B8F8-08ED5DEC8A5B}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -426,7 +440,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0%" sourceLinked="0"/>
@@ -507,7 +520,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1146" name="Imagem 3"/>
+        <xdr:cNvPr id="1146" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007A040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -570,7 +589,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1147" name="Gráfico 1"/>
+        <xdr:cNvPr id="1147" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007B040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -591,9 +616,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Escritório">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -631,9 +656,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Escritório">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -668,7 +693,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -703,7 +728,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Escritório">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -876,18 +901,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q622"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>27</v>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -997,7 +1027,7 @@
       </c>
       <c r="D10" s="1" t="str">
         <f ca="1">MID(CONCATENATE(REPT(B$4,B5),REPT(C$4,C5),REPT(D$4,D5)),RANDBETWEEN(1,SUM(B5:D5)),1)</f>
-        <v>R</v>
+        <v>B</v>
       </c>
       <c r="P10" s="1">
         <v>5</v>
@@ -1022,7 +1052,7 @@
       </c>
       <c r="B12" s="1">
         <f ca="1">B7+COUNTIF(D10:D11,"R")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1">
         <f ca="1">C7+COUNTIF(D10:D11,"G")</f>
@@ -1030,7 +1060,7 @@
       </c>
       <c r="D12" s="1">
         <f ca="1">D7+COUNTIF(D10:D11,"B")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
@@ -1044,7 +1074,7 @@
       </c>
       <c r="D15" s="1" t="str">
         <f ca="1">MID(CONCATENATE(REPT(B$4,B12),REPT(C$4,C12),REPT(D$4,D12)),RANDBETWEEN(1,SUM(B12:D12)),1)</f>
-        <v>B</v>
+        <v>G</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
@@ -1053,15 +1083,15 @@
       </c>
       <c r="B16" s="1">
         <f ca="1">B12-IF(D15="R",1,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="1">
         <f ca="1">C12-IF(D15="G",1,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="1">
         <f ca="1">D12-IF(D15="B",1,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
@@ -1070,7 +1100,7 @@
       </c>
       <c r="D17" s="1" t="str">
         <f ca="1">MID(CONCATENATE(REPT(B$4,B16),REPT(C$4,C16),REPT(D$4,D16)),RANDBETWEEN(1,SUM(B16:D16)),1)</f>
-        <v>B</v>
+        <v>G</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
@@ -1115,11 +1145,11 @@
       </c>
       <c r="C22" s="1">
         <f ca="1">C5+IF(D21="A",COUNTIF(D15:D17,"G"),0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="1">
         <f ca="1">D5+IF(D21="A",COUNTIF(D15:D17,"B"),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1240,7 +1270,7 @@
       </c>
       <c r="D28" s="1" t="str">
         <f ca="1">MID(CONCATENATE(REPT(B$4,B27),REPT(C$4,C27),REPT(D$4,D27)),RANDBETWEEN(1,SUM(B27:D27)),1)</f>
-        <v>B</v>
+        <v>G</v>
       </c>
       <c r="E28" s="1"/>
       <c r="G28" s="1"/>
@@ -1263,11 +1293,11 @@
       </c>
       <c r="C29" s="1">
         <f ca="1">C27-IF(D28="G",1,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="1">
         <f ca="1">D27-IF(D28="B",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="1"/>
       <c r="G29" s="1"/>
@@ -1308,11 +1338,11 @@
       </c>
       <c r="C31" s="1">
         <f ca="1">C29-IF(D30="G",1,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" s="1">
         <f ca="1">D29-IF(D30="B",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="1"/>
       <c r="G31" s="1"/>
@@ -1353,11 +1383,11 @@
       </c>
       <c r="C33" s="1">
         <f ca="1">C31-IF(D32="G",1,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" s="1">
         <f ca="1">D31-IF(D32="B",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="1"/>
       <c r="G33" s="1"/>
@@ -1375,7 +1405,7 @@
       </c>
       <c r="D34" s="1" t="str">
         <f ca="1">MID(CONCATENATE(REPT(B$4,B33),REPT(C$4,C33),REPT(D$4,D33)),RANDBETWEEN(1,SUM(B33:D33)),1)</f>
-        <v>G</v>
+        <v>B</v>
       </c>
       <c r="E34" s="1"/>
       <c r="G34" s="1"/>
@@ -1420,7 +1450,7 @@
       </c>
       <c r="D36" s="1" t="str">
         <f ca="1">MID(CONCATENATE(REPT(B$4,B35),REPT(C$4,C35),REPT(D$4,D35)),RANDBETWEEN(1,SUM(B35:D35)),1)</f>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="E36" s="1"/>
       <c r="G36" s="1"/>
@@ -1438,11 +1468,11 @@
       </c>
       <c r="B37" s="1">
         <f ca="1">COUNTIF(D28:D36,"R")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" s="1">
         <f ca="1">COUNTIF(D28:D36,"G")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" s="1">
         <f ca="1">COUNTIF(D28:D36,"B")</f>
@@ -9080,7 +9110,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E10001"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>

--- a/xls/Simulacao_exemplo2.xlsx
+++ b/xls/Simulacao_exemplo2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\OneDrive\Documentos\estatistica2025\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2026/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D0E5AC-7E3A-4DE3-BAE8-F6F85CA4D205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{92D0E5AC-7E3A-4DE3-BAE8-F6F85CA4D205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A443C71B-0C57-429F-88FC-4056DEFE8758}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="2085" windowWidth="26610" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exemplo 2" sheetId="9" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>Urna A</t>
   </si>
@@ -117,13 +117,10 @@
     <t>FR</t>
   </si>
   <si>
-    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2025</t>
+    <t>#https://cdrenno.github.io/Estatistica/</t>
   </si>
   <si>
-    <t>#http://urlib.net/8JMKD2USNRW34T/4D6DMD2</t>
-  </si>
-  <si>
-    <t>#https://cdrenno.github.io/Estatistica/</t>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2026</t>
   </si>
 </sst>
 </file>
@@ -907,17 +904,12 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -1074,7 +1066,7 @@
       </c>
       <c r="D15" s="1" t="str">
         <f ca="1">MID(CONCATENATE(REPT(B$4,B12),REPT(C$4,C12),REPT(D$4,D12)),RANDBETWEEN(1,SUM(B12:D12)),1)</f>
-        <v>G</v>
+        <v>B</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
@@ -1087,11 +1079,11 @@
       </c>
       <c r="C16" s="1">
         <f ca="1">C12-IF(D15="G",1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="1">
         <f ca="1">D12-IF(D15="B",1,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
@@ -1100,7 +1092,7 @@
       </c>
       <c r="D17" s="1" t="str">
         <f ca="1">MID(CONCATENATE(REPT(B$4,B16),REPT(C$4,C16),REPT(D$4,D16)),RANDBETWEEN(1,SUM(B16:D16)),1)</f>
-        <v>G</v>
+        <v>B</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
@@ -1145,11 +1137,11 @@
       </c>
       <c r="C22" s="1">
         <f ca="1">C5+IF(D21="A",COUNTIF(D15:D17,"G"),0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="1">
         <f ca="1">D5+IF(D21="A",COUNTIF(D15:D17,"B"),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1208,7 +1200,7 @@
       </c>
       <c r="G25" s="7">
         <f ca="1">D37</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -1224,7 +1216,7 @@
       </c>
       <c r="D26" s="5" t="str">
         <f ca="1">IF(RAND() &lt; 0.5,"A","B")</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="E26" s="1"/>
       <c r="G26" s="3" t="s">
@@ -1241,19 +1233,19 @@
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
         <f ca="1">CONCATENATE("Urna ",D26)</f>
-        <v>Urna B</v>
+        <v>Urna A</v>
       </c>
       <c r="B27" s="1">
         <f ca="1">IF(D26="A",B22,B23)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" s="1">
         <f ca="1">IF(D26="A",C22,C23)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" s="1">
         <f ca="1">IF(D26="A",D22,D23)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -1270,7 +1262,7 @@
       </c>
       <c r="D28" s="1" t="str">
         <f ca="1">MID(CONCATENATE(REPT(B$4,B27),REPT(C$4,C27),REPT(D$4,D27)),RANDBETWEEN(1,SUM(B27:D27)),1)</f>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="E28" s="1"/>
       <c r="G28" s="1"/>
@@ -1285,19 +1277,19 @@
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
         <f ca="1">A27</f>
-        <v>Urna B</v>
+        <v>Urna A</v>
       </c>
       <c r="B29" s="1">
         <f ca="1">B27-IF(D28="R",1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="1">
         <f ca="1">C27-IF(D28="G",1,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" s="1">
         <f ca="1">D27-IF(D28="B",1,0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" s="1"/>
       <c r="G29" s="1"/>
@@ -1315,7 +1307,7 @@
       </c>
       <c r="D30" s="1" t="str">
         <f ca="1">MID(CONCATENATE(REPT(B$4,B29),REPT(C$4,C29),REPT(D$4,D29)),RANDBETWEEN(1,SUM(B29:D29)),1)</f>
-        <v>G</v>
+        <v>B</v>
       </c>
       <c r="E30" s="1"/>
       <c r="G30" s="1"/>
@@ -1330,19 +1322,19 @@
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
         <f ca="1">A27</f>
-        <v>Urna B</v>
+        <v>Urna A</v>
       </c>
       <c r="B31" s="1">
         <f ca="1">B29-IF(D30="R",1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" s="1">
         <f ca="1">C29-IF(D30="G",1,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="1">
         <f ca="1">D29-IF(D30="B",1,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" s="1"/>
       <c r="G31" s="1"/>
@@ -1360,7 +1352,7 @@
       </c>
       <c r="D32" s="1" t="str">
         <f ca="1">MID(CONCATENATE(REPT(B$4,B31),REPT(C$4,C31),REPT(D$4,D31)),RANDBETWEEN(1,SUM(B31:D31)),1)</f>
-        <v>G</v>
+        <v>B</v>
       </c>
       <c r="E32" s="1"/>
       <c r="G32" s="1"/>
@@ -1375,11 +1367,11 @@
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
         <f ca="1">A27</f>
-        <v>Urna B</v>
+        <v>Urna A</v>
       </c>
       <c r="B33" s="1">
         <f ca="1">B31-IF(D32="R",1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" s="1">
         <f ca="1">C31-IF(D32="G",1,0)</f>
@@ -1387,7 +1379,7 @@
       </c>
       <c r="D33" s="1">
         <f ca="1">D31-IF(D32="B",1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="1"/>
       <c r="G33" s="1"/>
@@ -1420,11 +1412,11 @@
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
         <f ca="1">A27</f>
-        <v>Urna B</v>
+        <v>Urna A</v>
       </c>
       <c r="B35" s="1">
         <f ca="1">B33-IF(D34="R",1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" s="1">
         <f ca="1">C33-IF(D34="G",1,0)</f>
@@ -1432,7 +1424,7 @@
       </c>
       <c r="D35" s="1">
         <f ca="1">D33-IF(D34="B",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="1"/>
       <c r="G35" s="1"/>
@@ -1450,7 +1442,7 @@
       </c>
       <c r="D36" s="1" t="str">
         <f ca="1">MID(CONCATENATE(REPT(B$4,B35),REPT(C$4,C35),REPT(D$4,D35)),RANDBETWEEN(1,SUM(B35:D35)),1)</f>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="E36" s="1"/>
       <c r="G36" s="1"/>
@@ -1472,11 +1464,11 @@
       </c>
       <c r="C37" s="1">
         <f ca="1">COUNTIF(D28:D36,"G")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D37" s="1">
         <f ca="1">COUNTIF(D28:D36,"B")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37" s="1"/>
       <c r="G37" s="1"/>
